--- a/branches/migration/2026.0.0-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
+++ b/branches/migration/2026.0.0-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T18:29:39+00:00</t>
+    <t>2026-08-31T18:40:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.0-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
+++ b/branches/migration/2026.0.0-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T18:40:24+00:00</t>
+    <t>2026-08-31T19:25:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.0-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
+++ b/branches/migration/2026.0.0-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T19:25:28+00:00</t>
+    <t>2026-08-31T19:40:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.0-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
+++ b/branches/migration/2026.0.0-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T19:40:07+00:00</t>
+    <t>2026-08-31T20:03:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.0-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
+++ b/branches/migration/2026.0.0-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:03:15+00:00</t>
+    <t>2026-08-31T20:24:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.0-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
+++ b/branches/migration/2026.0.0-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.0</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:24:02+00:00</t>
+    <t>2026-08-31T20:56:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.0-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
+++ b/branches/migration/2026.0.0-template-v0.13.2/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:56:51+00:00</t>
+    <t>2026-08-31T21:06:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
